--- a/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Summary.xlsx
+++ b/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Summary.xlsx
@@ -32,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="221">
-  <si>
-    <t xml:space="preserve">Job #2108 · R&amp;G Apartments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cortex JCR Summary  •  Braseth Construction (Owner: TBD)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="224">
+  <si>
+    <t xml:space="preserve">Job #2108 · R&amp;G Apartments (Rainier &amp; Genesee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cortex JCR Summary  •  Braseth Construction (Owner: Lake Union Partners)</t>
   </si>
   <si>
     <t xml:space="preserve">PROJECT OVERVIEW</t>
@@ -52,25 +52,25 @@
     <t xml:space="preserve">Project Name:</t>
   </si>
   <si>
-    <t xml:space="preserve">R&amp;G Apartments</t>
+    <t xml:space="preserve">R&amp;G Apartments (Rainier &amp; Genesee)</t>
   </si>
   <si>
     <t xml:space="preserve">General Contractor</t>
   </si>
   <si>
-    <t xml:space="preserve">Braseth Construction (Owner: TBD)</t>
+    <t xml:space="preserve">Braseth Construction (Owner: Lake Union Partners)</t>
   </si>
   <si>
     <t xml:space="preserve">Location</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD</t>
+    <t xml:space="preserve">Rainier Ave S × S Genesee St, Seattle WA (Columbia City corridor / South Seattle)</t>
   </si>
   <si>
     <t xml:space="preserve">Project Duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 2027 (estimated) – TBD (Pre-construction — on hold)</t>
+    <t xml:space="preserve">Summer 2026 / Q1 2027 (target · pending Braseth go-ahead) – TBD (Pre-construction · ON HOLD · est. 28 months once activated)</t>
   </si>
   <si>
     <t xml:space="preserve">Status</t>
@@ -160,9 +160,15 @@
     <t xml:space="preserve">Total Fixtures</t>
   </si>
   <si>
+    <t xml:space="preserve">TBD (no Job Ticket — pre-construction)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fixtures / Unit</t>
   </si>
   <si>
+    <t xml:space="preserve">Estimated ~4.5 (per #2061 Alta Columbia City benchmark)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GC</t>
   </si>
   <si>
@@ -172,6 +178,9 @@
     <t xml:space="preserve">Owner</t>
   </si>
   <si>
+    <t xml:space="preserve">Lake Union Partners</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurance</t>
   </si>
   <si>
@@ -181,7 +190,7 @@
     <t xml:space="preserve">Duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-construction — on hold</t>
+    <t xml:space="preserve">Pre-construction · ON HOLD · est. 28 months once activated</t>
   </si>
   <si>
     <t xml:space="preserve">Permit</t>
@@ -193,13 +202,13 @@
     <t xml:space="preserve">NARRATIVE</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-construction project — on hold pending Braseth go-ahead. OWP has sunk $117k of design + takeoff cost (Franklin Engineering $90.6k MEP design fee + $6.4k permit + $2.1k takeoff labor + $922 equipment + $1.2k burden). Only $91.4k has been billed. Carrying loss of $25.8k if project doesn't activate. Reach out to Braseth PM to confirm summer 2026 start before Q4 2026.</t>
+    <t xml:space="preserve">Pre-construction · ON HOLD pending Braseth go-ahead. OWP has been pursuing this project since 2021, originally as 'Rainier &amp; Genesee' with BMDC at 226 units / $5.15M. Project redesigned + re-released late 2024 with Braseth as GC, expanded to 263 units, OWP rebid at $4.46M (-13.4% from 2021 despite +16% unit growth). Final revised BID Feb 2025 at $4,619,052. Project then went on hold. To date OWP has billed $91,402 against $117,162 sunk design+takeoff cost = -$25,760 carrying loss. $90,629 of sunk cost is the Franklin Engineering MEP design-build fee (92.5% of OWP's $97k AP). Lake Union Partners is OWP's repeat owner at the Rainier corridor — same as #2061 Alta Columbia City (where OWP delivered 41.4% margin). Strong positive risk indicator. New GC (Braseth) — OWP has 0 closed-job history. If activated, watch payment + CO behavior closely.</t>
   </si>
   <si>
     <t xml:space="preserve">SOURCES</t>
   </si>
   <si>
-    <t xml:space="preserve">Job #2108 — R&amp;G Apartments  •  GC: Braseth Construction  •  Status: ON HOLD · Summer 2026?</t>
+    <t xml:space="preserve">Job #2108 — R&amp;G Apartments (Rainier &amp; Genesee)  •  GC: Braseth Construction  •  Status: ON HOLD · Summer 2026?</t>
   </si>
   <si>
     <t xml:space="preserve">Canonical source: 2108_data.json (Sage Timberline JDR · Apr 3 2026 run)</t>
@@ -208,16 +217,16 @@
     <t xml:space="preserve">Dashboard arrays: 2108_dashboard_arrays.json (mirrors index.html PROJECTS['2108'])</t>
   </si>
   <si>
-    <t xml:space="preserve">Project profile: 263 units · TBD · Pre-construction — on hold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design team: Franklin Engineering (MEP per AP $90.6k design fee)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract: Not yet executed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billing: No pay apps filed (only $91k design billing)</t>
+    <t xml:space="preserve">Project profile: 263 units · Rainier Ave S × S Genesee St, Seattle WA (Columbia City corridor / South Seattle) · Pre-construction · ON HOLD · est. 28 months once activated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design team: Skb Architects (architect), Emerald City Engineering (bridge MEP), Franklin Engineering (OWP design-build engineer · $90.6k design fee booked)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract: Subcontract NOT yet executed — final BID submitted Feb 27 2025 ($4,619,052 / 263 units). Bid history: 2021 BMDC budget at 226u/$5.15M → 2024 Braseth bid at 263u/$4.46M → 2025 final BID +3.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing: $91,402 billed across 4 progress billings (takeoff phase). $0 retention.</t>
   </si>
   <si>
     <t xml:space="preserve">Permit: Pre-permit</t>
@@ -877,80 +886,76 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1209,472 +1214,472 @@
   <dimension ref="B2:I49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="8"/>
+      <c r="I14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="9"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="11" t="n">
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>2134</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="10" t="n">
         <f aca="false">C20-D20</f>
         <v>-2134</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="10" t="n">
         <f aca="false">IF(C20=0,0,D20/C20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="10" t="n">
         <f aca="false">IF($D$24=0,0,D20/$D$24)</f>
         <v>0.0182140967207798</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="11" t="n">
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <f aca="false">C21-D21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="10" t="n">
         <f aca="false">IF(C21=0,0,D21/C21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="10" t="n">
         <f aca="false">IF($D$24=0,0,D21/$D$24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="11" t="n">
+      <c r="C22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>113812</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <f aca="false">C22-D22</f>
         <v>-113812</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="10" t="n">
         <f aca="false">IF(C22=0,0,D22/C22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="10" t="n">
         <f aca="false">IF($D$24=0,0,D22/$D$24)</f>
         <v>0.9714071115208</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="11" t="n">
+      <c r="C23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>1216</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="10" t="n">
         <f aca="false">C23-D23</f>
         <v>-1216</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="10" t="n">
         <f aca="false">IF(C23=0,0,D23/C23)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="10" t="n">
         <f aca="false">IF($D$24=0,0,D23/$D$24)</f>
         <v>0.01037879175842</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="4" t="n">
         <f aca="false">SUM(C20:C23)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="4" t="n">
         <f aca="false">SUM(D20:D23)</f>
         <v>117162</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="4" t="n">
         <f aca="false">C24-D24</f>
         <v>-117162</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="4" t="n">
         <f aca="false">IF(C24=0,0,D24/C24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="10" t="n">
         <v>263</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="5" t="s">
+      <c r="E28" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>10</v>
+      <c r="F28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="C29" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="D29" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="E29" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="11" t="s">
+      <c r="D30" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="E30" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
-        <v>52</v>
+      <c r="B33" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
+      <c r="B34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="4" t="s">
-        <v>54</v>
+      <c r="B41" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="3" t="s">
-        <v>55</v>
+      <c r="B42" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="3" t="s">
-        <v>56</v>
+      <c r="B43" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="3" t="s">
-        <v>57</v>
+      <c r="B44" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="3" t="s">
-        <v>58</v>
+      <c r="B45" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="3" t="s">
-        <v>59</v>
+      <c r="B46" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="3" t="s">
-        <v>60</v>
+      <c r="B47" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="3" t="s">
-        <v>61</v>
+      <c r="B48" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="3" t="s">
-        <v>62</v>
+      <c r="B49" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1717,180 +1722,180 @@
   <dimension ref="B2:D25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="80"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>160</v>
+      <c r="B2" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>162</v>
+      <c r="B4" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>164</v>
+      <c r="C5" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>166</v>
+      <c r="C6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>168</v>
+      <c r="C7" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>170</v>
+      <c r="C8" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>172</v>
+      <c r="C9" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>174</v>
+      <c r="C10" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>176</v>
+      <c r="C11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>178</v>
+      <c r="C12" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>180</v>
+      <c r="C13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>182</v>
+      <c r="C14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>54</v>
+      <c r="B17" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>55</v>
+      <c r="B18" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>56</v>
+      <c r="B19" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>57</v>
+      <c r="B20" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>58</v>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>59</v>
+      <c r="B22" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>60</v>
+      <c r="B23" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>61</v>
+      <c r="B24" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>62</v>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1912,163 +1917,163 @@
   <dimension ref="B2:F20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>183</v>
+      <c r="B2" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="C4" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="11" t="s">
+      <c r="B5" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>192</v>
       </c>
+      <c r="D5" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>192</v>
+      <c r="B6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="B8" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>192</v>
+      <c r="C8" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="B9" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="C9" s="10" t="s">
         <v>205</v>
       </c>
+      <c r="D9" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>54</v>
+      <c r="B12" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>55</v>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>56</v>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>57</v>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>58</v>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>59</v>
+      <c r="B17" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>60</v>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>61</v>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>62</v>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2090,161 +2095,161 @@
   <dimension ref="B2:F20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>206</v>
+      <c r="B2" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>212</v>
+      <c r="B5" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>192</v>
+      <c r="E6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>212</v>
+      <c r="F7" s="17" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="B9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>192</v>
+      <c r="E9" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>54</v>
+      <c r="B12" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>55</v>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>56</v>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>57</v>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>58</v>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>59</v>
+      <c r="B17" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>60</v>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>61</v>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>62</v>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2266,138 +2271,138 @@
   <dimension ref="B2:G18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>218</v>
+      <c r="B2" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="B4" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>219</v>
+      <c r="D4" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="C5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>90629</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>220</v>
+      <c r="F5" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="C6" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>6402</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="3"/>
+      <c r="F6" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>922</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G7" s="3"/>
+      <c r="F7" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>54</v>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>55</v>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
-        <v>56</v>
+      <c r="B12" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>57</v>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>58</v>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>59</v>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>60</v>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>61</v>
+      <c r="B17" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>62</v>
+      <c r="B18" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2419,262 +2424,262 @@
   <dimension ref="B2:H26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>63</v>
+      <c r="B2" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="C4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>68</v>
+      <c r="H4" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
-        <v>69</v>
+      <c r="B5" s="12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="B6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>2134</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <f aca="false">E6-F6</f>
         <v>-2134</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="10" t="n">
         <f aca="false">IF(E6=0,0,F6/E6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>72</v>
+      <c r="B7" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="B8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>106488</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="10" t="n">
         <f aca="false">E8-F8</f>
         <v>-106488</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="10" t="n">
         <f aca="false">IF(E8=0,0,F8/E8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="B9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>922</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="10" t="n">
         <f aca="false">E9-F9</f>
         <v>-922</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="10" t="n">
         <f aca="false">IF(E9=0,0,F9/E9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="B10" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>6402</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="10" t="n">
         <f aca="false">E10-F10</f>
         <v>-6402</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="10" t="n">
         <f aca="false">IF(E10=0,0,F10/E10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
-        <v>79</v>
+      <c r="B11" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="B12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>1052</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="10" t="n">
         <f aca="false">E12-F12</f>
         <v>-1052</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="10" t="n">
         <f aca="false">IF(E12=0,0,F12/E12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="B13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>163</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="10" t="n">
         <f aca="false">E13-F13</f>
         <v>-163</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="10" t="n">
         <f aca="false">IF(E13=0,0,F13/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="B15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>117161.97</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="4" t="n">
         <v>117161.97</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="4" t="n">
         <v>117161.97</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
-        <v>54</v>
+      <c r="B18" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>55</v>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>56</v>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>57</v>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>58</v>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>59</v>
+      <c r="B23" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>60</v>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>61</v>
+      <c r="B25" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>62</v>
+      <c r="B26" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2696,348 +2701,348 @@
   <dimension ref="B2:H33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>85</v>
+      <c r="B2" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>86</v>
+      <c r="B4" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>2134</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <f aca="false">D6-E6</f>
         <v>-2134</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <f aca="false">IF(D6=0,0,E6/D6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="10" t="n">
         <f aca="false">IF(117162=0,0,E6/117162)</f>
         <v>0.0182140967207798</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>113812</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">D7-E7</f>
         <v>-113812</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="n">
         <f aca="false">IF(D7=0,0,E7/D7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="10" t="n">
         <f aca="false">IF(117162=0,0,E7/117162)</f>
         <v>0.9714071115208</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>1216</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">D8-E8</f>
         <v>-1216</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="10" t="n">
         <f aca="false">IF(D8=0,0,E8/D8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="10" t="n">
         <f aca="false">IF(117162=0,0,E8/117162)</f>
         <v>0.01037879175842</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>88</v>
+      <c r="B11" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="C12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>90</v>
+      <c r="F12" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="B13" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>106488</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <f aca="false">E13-D13</f>
         <v>106488</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="10" t="n">
         <f aca="false">IF(D13=0,0,F13/D13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="B14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>6402</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="10" t="n">
         <f aca="false">E14-D14</f>
         <v>6402</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="10" t="n">
         <f aca="false">IF(D14=0,0,F14/D14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11" t="n">
+      <c r="B15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>2134</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="10" t="n">
         <f aca="false">E15-D15</f>
         <v>2134</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="10" t="n">
         <f aca="false">IF(D15=0,0,F15/D15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="n">
+      <c r="B16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>1052</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="10" t="n">
         <f aca="false">E16-D16</f>
         <v>1052</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <f aca="false">IF(D16=0,0,F16/D16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="B17" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>922</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="10" t="n">
         <f aca="false">E17-D17</f>
         <v>922</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="10" t="n">
         <f aca="false">IF(D17=0,0,F17/D17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="B18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>163</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="10" t="n">
         <f aca="false">E18-D18</f>
         <v>163</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="10" t="n">
         <f aca="false">IF(D18=0,0,F18/D18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
-        <v>91</v>
+      <c r="B21" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3059,174 +3064,174 @@
   <dimension ref="B2:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>94</v>
+      <c r="B2" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>95</v>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
-        <v>96</v>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="C6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>97</v>
+      <c r="G6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>98</v>
+      <c r="B9" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="C10" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="11" t="n">
+      <c r="B11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>90629</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <f aca="false">IF(97953=0,0,D11/97953)</f>
         <v>0.925229446775494</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="11" t="n">
+      <c r="B12" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>6402</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <f aca="false">IF(97953=0,0,D12/97953)</f>
         <v>0.0653578757159046</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="11" t="n">
+      <c r="B13" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>922</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <f aca="false">IF(97953=0,0,D13/97953)</f>
         <v>0.00941267750860106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <f aca="false">SUM(C11:C13)</f>
         <v>12</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="4" t="n">
         <f aca="false">SUM(D11:D13)</f>
         <v>97953</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>54</v>
+      <c r="B17" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>55</v>
+      <c r="B18" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>56</v>
+      <c r="B19" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>57</v>
+      <c r="B20" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>58</v>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>59</v>
+      <c r="B22" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>60</v>
+      <c r="B23" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>61</v>
+      <c r="B24" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>62</v>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3248,114 +3253,114 @@
   <dimension ref="B2:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>106</v>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>111</v>
       </c>
+      <c r="D4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>1414</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">IF(C5=0,0,D5/C5)</f>
         <v>68.9756097560976</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>113</v>
+      <c r="F5" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="11" t="n">
+      <c r="B6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>720</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">IF(C6=0,0,D6/C6)</f>
         <v>60</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>113</v>
+      <c r="F6" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>54</v>
+      <c r="B9" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
-        <v>55</v>
+      <c r="B10" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>56</v>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
-        <v>57</v>
+      <c r="B12" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>58</v>
+      <c r="B13" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>59</v>
+      <c r="B14" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>60</v>
+      <c r="B15" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>61</v>
+      <c r="B16" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>62</v>
+      <c r="B17" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3377,151 +3382,151 @@
   <dimension ref="B2:F26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>115</v>
+      <c r="B2" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>32.5</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>2134</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>119</v>
+      <c r="F6" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>120</v>
+      <c r="B9" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="11" t="n">
+      <c r="B10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>65.66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="11" t="n">
+      <c r="B11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="11" t="n">
+      <c r="B12" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="10" t="n">
         <v>1.15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="11" t="n">
+      <c r="B13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="11" t="n">
+      <c r="B14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="11" t="n">
+      <c r="B15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="10" t="n">
         <v>16.2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
-        <v>54</v>
+      <c r="B18" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>55</v>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>56</v>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>57</v>
+      <c r="B21" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>58</v>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>59</v>
+      <c r="B23" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>60</v>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>61</v>
+      <c r="B25" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
-        <v>62</v>
+      <c r="B26" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3543,147 +3548,147 @@
   <dimension ref="B2:F25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>127</v>
+      <c r="B2" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
-        <v>62</v>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3705,147 +3710,147 @@
   <dimension ref="B2:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>143</v>
+      <c r="B2" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
-        <v>144</v>
+      <c r="B3" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="14" t="s">
+      <c r="B5" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>111</v>
+      <c r="D5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="C6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>90629</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>147</v>
+      <c r="F6" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>6402</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>147</v>
+      <c r="F7" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="C8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>922</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>147</v>
+      <c r="F8" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>54</v>
+      <c r="B11" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
-        <v>55</v>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>56</v>
+      <c r="B13" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>57</v>
+      <c r="B14" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>58</v>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>59</v>
+      <c r="B16" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>60</v>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>61</v>
+      <c r="B18" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>62</v>
+      <c r="B19" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3867,118 +3872,118 @@
   <dimension ref="B2:G23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>150</v>
+      <c r="B2" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>151</v>
+      <c r="B4" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>153</v>
+      <c r="B5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>153</v>
+      <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>153</v>
+      <c r="B7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>158</v>
+      <c r="B12" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="B13" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
-        <v>54</v>
+      <c r="B15" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>55</v>
+      <c r="B16" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>56</v>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
-        <v>57</v>
+      <c r="B18" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>58</v>
+      <c r="B19" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>59</v>
+      <c r="B20" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>60</v>
+      <c r="B21" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>61</v>
+      <c r="B22" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>62</v>
+      <c r="B23" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
